--- a/currentbuild/CodeSystem-decisiontemplate.xlsx
+++ b/currentbuild/CodeSystem-decisiontemplate.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="151">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:no-basis-auditevent/CodeSystem/decisiontemplate</t>
+    <t>https://terminology.dips.com/decisiontemplate</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-17T09:59:20+00:00</t>
+    <t>2024-04-06T16:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,14 +72,15 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Norway (https://github.com/HL7Norway)</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
-    <t>Dette er maler med ulike begrunnelser som kan benyttes som grunnlag for tilgang til pasientens journal ved sykehus som benytter DIPS som journalsystem.
-Er definert her kun midlertidig. Vil bli flyttet til annen ala https://terminology.dips.com/decisiontemplate (under arbeid).</t>
+    <t xml:space="preserve">These are templates with various justifications that can be used as a basis for accessing the patient's medical record at hospitals that utilize DIPS as their journal system.
+Templates that user can select manually are marked as '(Eksplisitt mal)'.
+</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -112,7 +116,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>34</t>
+    <t>38</t>
   </si>
   <si>
     <t>Level</t>
@@ -130,69 +134,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>HENV_BEH</t>
-  </si>
-  <si>
-    <t>Henvendelse fra pasientens behandler</t>
-  </si>
-  <si>
-    <t>Henvendelse fra pasientens behandler.</t>
-  </si>
-  <si>
-    <t>HENV_PAA</t>
-  </si>
-  <si>
-    <t>Henvendelse fra pasientens pårørende</t>
-  </si>
-  <si>
-    <t>Henvendelse fra pasientens pårørende.</t>
-  </si>
-  <si>
-    <t>MELDT</t>
-  </si>
-  <si>
-    <t>Meldt pasient</t>
-  </si>
-  <si>
-    <t>Meldt pasient (for eksempel fra legevakta eller ambulansen).</t>
-  </si>
-  <si>
-    <t>BLAALYS</t>
-  </si>
-  <si>
-    <t>Blålys</t>
-  </si>
-  <si>
-    <t>Bruk av blålys - akutt helsehjelp</t>
-  </si>
-  <si>
-    <t>EKSTSVAR</t>
-  </si>
-  <si>
-    <t>Eksternt prøvesvar/notat til vurdering</t>
-  </si>
-  <si>
-    <t>Det er behov for å se på et eksternt prøvesvar eller notat som har kommet inn på pasienten</t>
-  </si>
-  <si>
-    <t>KVAL</t>
-  </si>
-  <si>
-    <t>Internkontroll/Kvalitetssikring</t>
-  </si>
-  <si>
-    <t>Noen ansatte har som oppgave å kontrollere koder og andre registreringer i DIPS, kanskje også se på hvordan det registreres/dokumenteres m.m uten at brukeren deltar i behandling av pasient.   Da kan denne beslutningsmalen brukes.</t>
-  </si>
-  <si>
-    <t>OPRPLAN</t>
-  </si>
-  <si>
-    <t>Pasienten finnes på operasjonsoversikten</t>
-  </si>
-  <si>
-    <t>Pasienten finnes på operasjonsoversikten i DIPS</t>
-  </si>
-  <si>
     <t>KONSSERIE</t>
   </si>
   <si>
@@ -223,7 +164,7 @@
     <t>IT-Systemarbeid</t>
   </si>
   <si>
-    <t>IT systemarbeid er en besluttningsmal som kan benyttes for å gi tilgang til journaldata når it-personell (på sykehuset / eller personell fra DIPS ASA), må gjøre systemarbeid - feilretting o.l. - på journaldataene.</t>
+    <t>IT systemarbeid er en besluttningsmal som kan benyttes for å gi tilgang til journaldata når it-personell (på sykehuset / eller personell fra DIPS ASA), må gjøre systemarbeid - feilretting o.l. - på journaldataene. (Eksplisitt mal)</t>
   </si>
   <si>
     <t>TILSYN</t>
@@ -232,7 +173,7 @@
     <t>Tilsyn på annen avdeling.</t>
   </si>
   <si>
-    <t>"Tilsyn på annen avdeling" kan benyttes når en behandler bes om å foreta et tilsyn på en annen avdeling, og behandleren av den grunn ikke har ordinær tilgang til journalen.  Det kan angis hvilken rekvirent som har bedt om at tilsyn skal foretas.</t>
+    <t>"Tilsyn på annen avdeling" kan benyttes når en behandler bes om å foreta et tilsyn på en annen avdeling, og behandleren av den grunn ikke har ordinær tilgang til journalen.  Det kan angis hvilken rekvirent som har bedt om at tilsyn skal foretas. (Eksplisitt mal)</t>
   </si>
   <si>
     <t>ARBFLYT</t>
@@ -241,7 +182,7 @@
     <t>Oppgave i arbeidsflyt</t>
   </si>
   <si>
-    <t>Beslutning som slår til dersom det finnes en ikke utført oppgave i arbeidsflyt.  Gjelder alle oppgavetyper.</t>
+    <t xml:space="preserve">Beslutning som slår til dersom det finnes en ikke utført oppgave i arbeidsflyt.  Gjelder alle oppgavetyper.  </t>
   </si>
   <si>
     <t>BEHANDLER</t>
@@ -298,10 +239,10 @@
     <t>BELEGG</t>
   </si>
   <si>
-    <t>Inneliggende pasient</t>
-  </si>
-  <si>
-    <t>Pasienten er inneliggende.</t>
+    <t>Innlagt pasient</t>
+  </si>
+  <si>
+    <t>Pasienten er innlagt.</t>
   </si>
   <si>
     <t>PLANOPP</t>
@@ -328,7 +269,7 @@
     <t>Tilsyn med helsepersonellets virksomhet</t>
   </si>
   <si>
-    <t>Tilsyn med helsepersonellets virksomhet.</t>
+    <t>Tilsyn med helsepersonellets virksomhet. (Eksplisitt mal)</t>
   </si>
   <si>
     <t>INNSYN</t>
@@ -337,7 +278,7 @@
     <t>Pasientinnsyn</t>
   </si>
   <si>
-    <t>Pasientens innsyn i egen journal.</t>
+    <t>Pasientens innsyn i egen journal. (Eksplisitt mal)</t>
   </si>
   <si>
     <t>OFFBEST</t>
@@ -346,7 +287,7 @@
     <t>Bestilling av dokumenter fra offentlige og juridiske instanser og forsikringselskap</t>
   </si>
   <si>
-    <t>Bestilling av dokumenter fra offentlige og juridiske instanser og forsikringselskap.</t>
+    <t>Bestilling av dokumenter fra offentlige og juridiske instanser og forsikringselskap. (Eksplisitt mal)</t>
   </si>
   <si>
     <t>HENV_PAS</t>
@@ -355,7 +296,7 @@
     <t>Henvendelse fra pasienten</t>
   </si>
   <si>
-    <t>Henvendelse fra pasienten selv.</t>
+    <t>Henvendelse fra pasienten selv. (Eksplisitt mal)</t>
   </si>
   <si>
     <t>HENVPER</t>
@@ -385,13 +326,67 @@
     <t>Bruker er pasientens primærkontakt.</t>
   </si>
   <si>
+    <t>HENV_BEH</t>
+  </si>
+  <si>
+    <t>Henvendelse fra pasientens behandler</t>
+  </si>
+  <si>
+    <t>Henvendelse fra pasientens behandler. (Eksplisitt mal)</t>
+  </si>
+  <si>
+    <t>HENV_PAA</t>
+  </si>
+  <si>
+    <t>Henvendelse fra pasientens pårørende</t>
+  </si>
+  <si>
+    <t>Henvendelse fra pasientens pårørende. (Eksplisitt mal)</t>
+  </si>
+  <si>
+    <t>MELDT</t>
+  </si>
+  <si>
+    <t>Meldt pasient</t>
+  </si>
+  <si>
+    <t>Meldt pasient (for eksempel fra legevakta eller ambulansen). (Eksplisitt mal)</t>
+  </si>
+  <si>
+    <t>EKSTSVAR</t>
+  </si>
+  <si>
+    <t>Eksternt prøvesvar/notat til vurdering</t>
+  </si>
+  <si>
+    <t>Det er behov for å se på et eksternt prøvesvar eller notat som har kommet inn på pasienten (Eksplisitt mal)</t>
+  </si>
+  <si>
+    <t>OPRPLAN</t>
+  </si>
+  <si>
+    <t>Pasienten finnes på operasjonsoversikten</t>
+  </si>
+  <si>
+    <t>Pasienten finnes på operasjonsoversikten i DIPS</t>
+  </si>
+  <si>
+    <t>EGENLAER</t>
+  </si>
+  <si>
+    <t>Egen læring/kvalitetssikring av gitt behandling</t>
+  </si>
+  <si>
+    <t>Begrunnelse forankret i Helsepersonellovens §29 c (Eksplisitt mal)</t>
+  </si>
+  <si>
     <t>DELBEHAN</t>
   </si>
   <si>
     <t>Deltar i behandlingen av pasienten</t>
   </si>
   <si>
-    <t>Deltar i behandlingen av pasienten.</t>
+    <t>Deltar i behandlingen av pasienten. (Eksplisitt mal)</t>
   </si>
   <si>
     <t>TILSYN3</t>
@@ -400,7 +395,67 @@
     <t>Statlig tilsyn</t>
   </si>
   <si>
-    <t>Statlig tilsyn er forankret i  Helsetilsynsloven, Spesialisthelsetjenesteloven §6-2 og Pasientjournalloven §26.</t>
+    <t>Statlig tilsyn er forankret i  Helsetilsynsloven, Spesialisthelsetjenesteloven §6-2 og Pasientjournalloven §26. (Eksplisitt mal)</t>
+  </si>
+  <si>
+    <t>BLAALYS</t>
+  </si>
+  <si>
+    <t>Blålys</t>
+  </si>
+  <si>
+    <t>Bruk av blålys - akutt helsehjelp (Eksplisitt mal)</t>
+  </si>
+  <si>
+    <t>KVAL</t>
+  </si>
+  <si>
+    <t>Internkontroll/Kvalitetssikring</t>
+  </si>
+  <si>
+    <t>Noen ansatte har som oppgave å kontrollere koder og andre registreringer i DIPS, kanskje også se på hvordan det registreres/dokumenteres m.m uten at brukeren deltar i behandling av pasient.   Da kan denne beslutningsmalen brukes. (Eksplisitt mal)</t>
+  </si>
+  <si>
+    <t>FORSK</t>
+  </si>
+  <si>
+    <t>Forskning</t>
+  </si>
+  <si>
+    <t>"Forskning" er en beslutningsmal som kan benyttes for å gi tilgang til pasientdata i forbindelse med Forskning. (Eksplisitt mal)</t>
+  </si>
+  <si>
+    <t>ETTERARB</t>
+  </si>
+  <si>
+    <t>Etterarbeide</t>
+  </si>
+  <si>
+    <t>"Etterarbeide" er en beslutningsmal som kan benyttes for å gi tilgang til pasientdata i forbindelse med Etterarbeide. (Eksplisitt mal)</t>
+  </si>
+  <si>
+    <t>UNDERVISN</t>
+  </si>
+  <si>
+    <t>Undervisning</t>
+  </si>
+  <si>
+    <t>"Undervisning" er en besluttningsmal som kan benyttes for å gi tilgang til pasientdata i forbindelse med undervisning. (Eksplisitt mal)</t>
+  </si>
+  <si>
+    <t>NYPAS</t>
+  </si>
+  <si>
+    <t>Pasientadministrasjon</t>
+  </si>
+  <si>
+    <t>Pasientadministrasjon, f.eks registrering av ny pasient</t>
+  </si>
+  <si>
+    <t>ROLPAS</t>
+  </si>
+  <si>
+    <t>Bruker har rolle overfor pasient</t>
   </si>
   <si>
     <t>HHJELANPAS</t>
@@ -409,31 +464,16 @@
     <t>Yte helsehjelp til annen pasient</t>
   </si>
   <si>
-    <t>"Yte helsehjelp til annen pasient" kan benyttes for å gi tilgang til pasientopplysninger på en pasient for å yte helsehjelp til annen pasient, jf. helsepersonelloven §25 b.</t>
-  </si>
-  <si>
-    <t>NYPAS</t>
-  </si>
-  <si>
-    <t>Pasientadministrasjon</t>
-  </si>
-  <si>
-    <t>Pasientadministrasjon, f.eks registrering av ny pasient</t>
-  </si>
-  <si>
-    <t>ROLPAS</t>
-  </si>
-  <si>
-    <t>Bruker har rolle overfor pasient</t>
-  </si>
-  <si>
-    <t>EGENLAER</t>
-  </si>
-  <si>
-    <t>Egen læring/kvalitetssikring av gitt behandling</t>
-  </si>
-  <si>
-    <t>Begrunnelse forankret i Helsepersonellovens §29 c</t>
+    <t>"Yte helsehjelp til annen pasient" kan benyttes for å gi tilgang til pasientopplysninger på en pasient for å yte helsehjelp til annen pasient, jf. helsepersonelloven §25 b. (Eksplisitt mal)</t>
+  </si>
+  <si>
+    <t>PASADM</t>
+  </si>
+  <si>
+    <t>Administrasjon</t>
+  </si>
+  <si>
+    <t>For administrative oppgaver som feks skanning av dokumenter, endring av pasientopplysninger, kodekontroll o.l.</t>
   </si>
 </sst>
 </file>
@@ -626,102 +666,106 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -731,32 +775,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s" s="2">
         <v>40</v>
@@ -764,7 +808,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s" s="2">
         <v>41</v>
@@ -778,7 +822,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>44</v>
@@ -792,7 +836,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>47</v>
@@ -806,7 +850,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s" s="2">
         <v>50</v>
@@ -820,7 +864,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s" s="2">
         <v>53</v>
@@ -834,7 +878,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s" s="2">
         <v>56</v>
@@ -848,7 +892,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s" s="2">
         <v>59</v>
@@ -857,371 +901,427 @@
         <v>60</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/currentbuild/CodeSystem-decisiontemplate.xlsx
+++ b/currentbuild/CodeSystem-decisiontemplate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-06T16:49:55+00:00</t>
+    <t>2024-04-28T16:36:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
   </si>
   <si>
     <t xml:space="preserve">These are templates with various justifications that can be used as a basis for accessing the patient's medical record at hospitals that utilize DIPS as their journal system.
-Templates that user can select manually are marked as '(Eksplisitt mal)'.
+Templates that user, if authorized, can select manually as reason for accessing patient's medical record are marked as '(Eksplisitt mal)'.
 </t>
   </si>
   <si>

--- a/currentbuild/CodeSystem-decisiontemplate.xlsx
+++ b/currentbuild/CodeSystem-decisiontemplate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-28T16:36:28+00:00</t>
+    <t>2024-06-04T05:44:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-decisiontemplate.xlsx
+++ b/currentbuild/CodeSystem-decisiontemplate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T05:44:14+00:00</t>
+    <t>2024-06-04T06:11:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-decisiontemplate.xlsx
+++ b/currentbuild/CodeSystem-decisiontemplate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T06:11:20+00:00</t>
+    <t>2024-06-06T18:49:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-decisiontemplate.xlsx
+++ b/currentbuild/CodeSystem-decisiontemplate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>0.9.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-06T18:49:12+00:00</t>
+    <t>2024-06-11T05:22:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-decisiontemplate.xlsx
+++ b/currentbuild/CodeSystem-decisiontemplate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:22:30+00:00</t>
+    <t>2024-06-11T05:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
